--- a/data/employees/EMP085/AST-EMP085-06.xlsx
+++ b/data/employees/EMP085/AST-EMP085-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor Comparison - Casey Lee (Procurement)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Casey Lee | Role: Senior Engineer | Location: Bengaluru | Date: 2025-04-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>On-Time %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Quality %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Spend YTD ($K)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>61</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme Components</t>
+          <t>EMP085</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>97</v>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1450</v>
+        <v>93</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GlobalParts Inc</t>
+          <t>EMP085</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91</v>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
-      </c>
-      <c r="F6" t="n">
-        <v>820</v>
+        <v>62</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TechSupply Co</t>
+          <t>EMP085</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>99</v>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2100</v>
+        <v>61</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CleanRoom Solutions</t>
+          <t>EMP085</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumables</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D8" t="n">
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>68</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>93</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>84</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>90</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>70</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>86</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>79</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>68</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>88</v>
       </c>
-      <c r="E8" t="n">
-        <v>95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>340</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>97</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>82</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>80</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp085 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP085</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP085 contributes to ast emp085 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>